--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2206-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2206-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C515BC21-1CDA-4B7E-8FCE-0C098B209197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{663A8D08-8B55-4EBD-B664-FC2762EDCDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{57763E18-C7D2-4DCA-B597-05B53069FCE2}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DDE85FCF-42DA-4BEA-A5A8-D7A85869AB1A}"/>
   </bookViews>
   <sheets>
     <sheet name="2206-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1598,28 +1598,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC89AEC-FC25-49C2-A151-9FD0398E0E57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675F882C-0602-42C7-94AA-D911514B15C6}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1653,7 +1653,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1689,7 +1689,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1809,7 +1809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2023</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2022</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2021</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2020</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2019</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2018</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2017</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2016</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2015</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2014</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2013</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>2012</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2011</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="43">
         <v>2010</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
       <c r="C40" s="20" t="s">
@@ -4395,7 +4395,7 @@
       <c r="W40" s="52"/>
       <c r="X40" s="48"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2009</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>2008</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>2007</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="55"/>
       <c r="B44" s="56"/>
       <c r="C44" s="22" t="s">
@@ -4639,7 +4639,7 @@
       <c r="W44" s="62"/>
       <c r="X44" s="58"/>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="41">
         <v>2006</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>2005</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>2004</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>2003</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>2002</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>2001</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>2000</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>1999</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="55"/>
       <c r="B53" s="56"/>
       <c r="C53" s="22" t="s">
@@ -5243,7 +5243,7 @@
       <c r="W53" s="62"/>
       <c r="X53" s="58"/>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="41">
         <v>1998</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>1997</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="41">
         <v>1996</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39">
         <v>1995</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="41">
         <v>1994</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="39">
         <v>1993</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="41">
         <v>1992</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="39" t="s">
         <v>63</v>
       </c>
